--- a/produccion/video02/plantilla/Distribuidora Sur.xlsx
+++ b/produccion/video02/plantilla/Distribuidora Sur.xlsx
@@ -15,6 +15,28 @@
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1433,8 +1455,8 @@
       <c r="B2" s="3" t="n">
         <v>46296</v>
       </c>
-      <c r="D2">
-        <f>IFERROR(_xlfn._xlws.SORT(_xlfn._xlws.FILTER(_xlfn.CHOOSECOLS(Pedidos!A2:M13,3,11,10),Pedidos!M2:M13="Vencido"),3,-1),"Sin vencidos")</f>
+      <c r="D2" cm="1">
+        <f t="array" ref="D2">IFERROR(_xlfn._xlws.SORT(_xlfn._xlws.FILTER(_xlfn.CHOOSECOLS(Pedidos!A2:M13,3,11,10),Pedidos!M2:M13="Vencido"),3,-1),"Sin vencidos")</f>
         <v/>
       </c>
       <c r="E2" s="3" t="n"/>
@@ -1488,8 +1510,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <f>_xlfn._xlws.SORT(_xlfn.UNIQUE(Pedidos!C2:C13))</f>
+      <c r="A8" cm="1">
+        <f t="array" ref="A8">_xlfn._xlws.SORT(_xlfn.UNIQUE(Pedidos!C2:C13))</f>
         <v/>
       </c>
       <c r="B8">

--- a/produccion/video02/plantilla/Distribuidora Sur.xlsx
+++ b/produccion/video02/plantilla/Distribuidora Sur.xlsx
@@ -9,8 +9,10 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Léeme" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pedidos" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Productos" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Productos" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompts" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Práctica" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -87,16 +89,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -486,7 +499,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Las fórmulas funcionan en Excel para la web (gratis) y en Excel 2021/365. No tiene macros ni vínculos externos.</t>
+          <t>Funciona en Excel para la web (gratis) y en Microsoft 365. En Excel 2021 fallan TEXTODESPUES (fórmula 3) y ELEGIRCOLS (fórmula 8); en 2016/2019, varias más. La fecha de corte de Resumen!B1 está fija (04/11/2026) para que veas los números del video: en tu planilla, escribe =HOY(). Sin macros ni vínculos externos. Respuestas generadas con Claude el 25/10/2026.</t>
         </is>
       </c>
     </row>
@@ -496,6 +509,1386 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="42.5" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="21.25" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="37.5" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Cliente (sistema)</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Vendedor (sistema)</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Vendedor</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Código</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Cant.</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Precio</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Desc.</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Neto</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>Vence</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ferretería el TORNILLO </t>
+        </is>
+      </c>
+      <c r="C2">
+        <f>PROPER(TRIM(B2))</f>
+        <v/>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>V01 | Diego Paz</t>
+        </is>
+      </c>
+      <c r="E2">
+        <f>_xlfn.TEXTAFTER(D2,"| ")</f>
+        <v/>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>LIM-010</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H2">
+        <f>_xlfn.XLOOKUP(F2,Productos!A:A,Productos!C:C,"Código no existe")</f>
+        <v/>
+      </c>
+      <c r="I2">
+        <f>_xlfn.IFS(G2*H2&gt;=100000,10%,G2*H2&gt;=40000,5%,TRUE,0)</f>
+        <v/>
+      </c>
+      <c r="J2">
+        <f>G2*H2*(1-I2)</f>
+        <v/>
+      </c>
+      <c r="K2" s="3">
+        <f>EOMONTH(A2,1)</f>
+        <v/>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M2">
+        <f>IF(L2="Sí","Cobrado",IF(K2&lt;Resumen!$B$1,"Vencido","Al día"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LIBRERÍA SAN MARTÍN SRL</t>
+        </is>
+      </c>
+      <c r="C3">
+        <f>PROPER(TRIM(B3))</f>
+        <v/>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>V02 | Carla Ruiz</t>
+        </is>
+      </c>
+      <c r="E3">
+        <f>_xlfn.TEXTAFTER(D3,"| ")</f>
+        <v/>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>PAP-200</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>120</v>
+      </c>
+      <c r="H3">
+        <f>_xlfn.XLOOKUP(F3,Productos!A:A,Productos!C:C,"Código no existe")</f>
+        <v/>
+      </c>
+      <c r="I3">
+        <f>_xlfn.IFS(G3*H3&gt;=100000,10%,G3*H3&gt;=40000,5%,TRUE,0)</f>
+        <v/>
+      </c>
+      <c r="J3">
+        <f>G3*H3*(1-I3)</f>
+        <v/>
+      </c>
+      <c r="K3" s="3">
+        <f>EOMONTH(A3,1)</f>
+        <v/>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M3">
+        <f>IF(L3="Sí","Cobrado",IF(K3&lt;Resumen!$B$1,"Vencido","Al día"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>kiosco la esquina</t>
+        </is>
+      </c>
+      <c r="C4">
+        <f>PROPER(TRIM(B4))</f>
+        <v/>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>V03 | Tomás Gil</t>
+        </is>
+      </c>
+      <c r="E4">
+        <f>_xlfn.TEXTAFTER(D4,"| ")</f>
+        <v/>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>LIM-020</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H4">
+        <f>_xlfn.XLOOKUP(F4,Productos!A:A,Productos!C:C,"Código no existe")</f>
+        <v/>
+      </c>
+      <c r="I4">
+        <f>_xlfn.IFS(G4*H4&gt;=100000,10%,G4*H4&gt;=40000,5%,TRUE,0)</f>
+        <v/>
+      </c>
+      <c r="J4">
+        <f>G4*H4*(1-I4)</f>
+        <v/>
+      </c>
+      <c r="K4" s="3">
+        <f>EOMONTH(A4,1)</f>
+        <v/>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M4">
+        <f>IF(L4="Sí","Cobrado",IF(K4&lt;Resumen!$B$1,"Vencido","Al día"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ferretería el tornillo  </t>
+        </is>
+      </c>
+      <c r="C5">
+        <f>PROPER(TRIM(B5))</f>
+        <v/>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>V01 | Diego Paz</t>
+        </is>
+      </c>
+      <c r="E5">
+        <f>_xlfn.TEXTAFTER(D5,"| ")</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>PAP-210</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>60</v>
+      </c>
+      <c r="H5">
+        <f>_xlfn.XLOOKUP(F5,Productos!A:A,Productos!C:C,"Código no existe")</f>
+        <v/>
+      </c>
+      <c r="I5">
+        <f>_xlfn.IFS(G5*H5&gt;=100000,10%,G5*H5&gt;=40000,5%,TRUE,0)</f>
+        <v/>
+      </c>
+      <c r="J5">
+        <f>G5*H5*(1-I5)</f>
+        <v/>
+      </c>
+      <c r="K5" s="3">
+        <f>EOMONTH(A5,1)</f>
+        <v/>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M5">
+        <f>IF(L5="Sí","Cobrado",IF(K5&lt;Resumen!$B$1,"Vencido","Al día"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Colegio Nuevo Horizonte</t>
+        </is>
+      </c>
+      <c r="C6">
+        <f>PROPER(TRIM(B6))</f>
+        <v/>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>V02 | Carla Ruiz</t>
+        </is>
+      </c>
+      <c r="E6">
+        <f>_xlfn.TEXTAFTER(D6,"| ")</f>
+        <v/>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>PAP-200</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>300</v>
+      </c>
+      <c r="H6">
+        <f>_xlfn.XLOOKUP(F6,Productos!A:A,Productos!C:C,"Código no existe")</f>
+        <v/>
+      </c>
+      <c r="I6">
+        <f>_xlfn.IFS(G6*H6&gt;=100000,10%,G6*H6&gt;=40000,5%,TRUE,0)</f>
+        <v/>
+      </c>
+      <c r="J6">
+        <f>G6*H6*(1-I6)</f>
+        <v/>
+      </c>
+      <c r="K6" s="3">
+        <f>EOMONTH(A6,1)</f>
+        <v/>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M6">
+        <f>IF(L6="Sí","Cobrado",IF(K6&lt;Resumen!$B$1,"Vencido","Al día"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>KIOSCO LA ESQUINA</t>
+        </is>
+      </c>
+      <c r="C7">
+        <f>PROPER(TRIM(B7))</f>
+        <v/>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>V03 | Tomás Gil</t>
+        </is>
+      </c>
+      <c r="E7">
+        <f>_xlfn.TEXTAFTER(D7,"| ")</f>
+        <v/>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>LIM-030</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>25</v>
+      </c>
+      <c r="H7">
+        <f>_xlfn.XLOOKUP(F7,Productos!A:A,Productos!C:C,"Código no existe")</f>
+        <v/>
+      </c>
+      <c r="I7">
+        <f>_xlfn.IFS(G7*H7&gt;=100000,10%,G7*H7&gt;=40000,5%,TRUE,0)</f>
+        <v/>
+      </c>
+      <c r="J7">
+        <f>G7*H7*(1-I7)</f>
+        <v/>
+      </c>
+      <c r="K7" s="3">
+        <f>EOMONTH(A7,1)</f>
+        <v/>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M7">
+        <f>IF(L7="Sí","Cobrado",IF(K7&lt;Resumen!$B$1,"Vencido","Al día"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">librería san martín srl </t>
+        </is>
+      </c>
+      <c r="C8">
+        <f>PROPER(TRIM(B8))</f>
+        <v/>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>V01 | Diego Paz</t>
+        </is>
+      </c>
+      <c r="E8">
+        <f>_xlfn.TEXTAFTER(D8,"| ")</f>
+        <v/>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>PAP-220</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>40</v>
+      </c>
+      <c r="H8">
+        <f>_xlfn.XLOOKUP(F8,Productos!A:A,Productos!C:C,"Código no existe")</f>
+        <v/>
+      </c>
+      <c r="I8">
+        <f>_xlfn.IFS(G8*H8&gt;=100000,10%,G8*H8&gt;=40000,5%,TRUE,0)</f>
+        <v/>
+      </c>
+      <c r="J8">
+        <f>G8*H8*(1-I8)</f>
+        <v/>
+      </c>
+      <c r="K8" s="3">
+        <f>EOMONTH(A8,1)</f>
+        <v/>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M8">
+        <f>IF(L8="Sí","Cobrado",IF(K8&lt;Resumen!$B$1,"Vencido","Al día"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Hotel  Mirador</t>
+        </is>
+      </c>
+      <c r="C9">
+        <f>PROPER(TRIM(B9))</f>
+        <v/>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>V01 | Diego Paz</t>
+        </is>
+      </c>
+      <c r="E9">
+        <f>_xlfn.TEXTAFTER(D9,"| ")</f>
+        <v/>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>LIM-040</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>12</v>
+      </c>
+      <c r="H9">
+        <f>_xlfn.XLOOKUP(F9,Productos!A:A,Productos!C:C,"Código no existe")</f>
+        <v/>
+      </c>
+      <c r="I9">
+        <f>_xlfn.IFS(G9*H9&gt;=100000,10%,G9*H9&gt;=40000,5%,TRUE,0)</f>
+        <v/>
+      </c>
+      <c r="J9">
+        <f>G9*H9*(1-I9)</f>
+        <v/>
+      </c>
+      <c r="K9" s="3">
+        <f>EOMONTH(A9,1)</f>
+        <v/>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M9">
+        <f>IF(L9="Sí","Cobrado",IF(K9&lt;Resumen!$B$1,"Vencido","Al día"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>colegio nuevo horizonte</t>
+        </is>
+      </c>
+      <c r="C10">
+        <f>PROPER(TRIM(B10))</f>
+        <v/>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>V02 | Carla Ruiz</t>
+        </is>
+      </c>
+      <c r="E10">
+        <f>_xlfn.TEXTAFTER(D10,"| ")</f>
+        <v/>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>PAP-220</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>150</v>
+      </c>
+      <c r="H10">
+        <f>_xlfn.XLOOKUP(F10,Productos!A:A,Productos!C:C,"Código no existe")</f>
+        <v/>
+      </c>
+      <c r="I10">
+        <f>_xlfn.IFS(G10*H10&gt;=100000,10%,G10*H10&gt;=40000,5%,TRUE,0)</f>
+        <v/>
+      </c>
+      <c r="J10">
+        <f>G10*H10*(1-I10)</f>
+        <v/>
+      </c>
+      <c r="K10" s="3">
+        <f>EOMONTH(A10,1)</f>
+        <v/>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M10">
+        <f>IF(L10="Sí","Cobrado",IF(K10&lt;Resumen!$B$1,"Vencido","Al día"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hotel mirador </t>
+        </is>
+      </c>
+      <c r="C11">
+        <f>PROPER(TRIM(B11))</f>
+        <v/>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>V03 | Tomás Gil</t>
+        </is>
+      </c>
+      <c r="E11">
+        <f>_xlfn.TEXTAFTER(D11,"| ")</f>
+        <v/>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>LIM-040</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>30</v>
+      </c>
+      <c r="H11">
+        <f>_xlfn.XLOOKUP(F11,Productos!A:A,Productos!C:C,"Código no existe")</f>
+        <v/>
+      </c>
+      <c r="I11">
+        <f>_xlfn.IFS(G11*H11&gt;=100000,10%,G11*H11&gt;=40000,5%,TRUE,0)</f>
+        <v/>
+      </c>
+      <c r="J11">
+        <f>G11*H11*(1-I11)</f>
+        <v/>
+      </c>
+      <c r="K11" s="3">
+        <f>EOMONTH(A11,1)</f>
+        <v/>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M11">
+        <f>IF(L11="Sí","Cobrado",IF(K11&lt;Resumen!$B$1,"Vencido","Al día"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kiosco La Esquina</t>
+        </is>
+      </c>
+      <c r="C12">
+        <f>PROPER(TRIM(B12))</f>
+        <v/>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>V01 | Diego Paz</t>
+        </is>
+      </c>
+      <c r="E12">
+        <f>_xlfn.TEXTAFTER(D12,"| ")</f>
+        <v/>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>PAP-210</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>10</v>
+      </c>
+      <c r="H12">
+        <f>_xlfn.XLOOKUP(F12,Productos!A:A,Productos!C:C,"Código no existe")</f>
+        <v/>
+      </c>
+      <c r="I12">
+        <f>_xlfn.IFS(G12*H12&gt;=100000,10%,G12*H12&gt;=40000,5%,TRUE,0)</f>
+        <v/>
+      </c>
+      <c r="J12">
+        <f>G12*H12*(1-I12)</f>
+        <v/>
+      </c>
+      <c r="K12" s="3">
+        <f>EOMONTH(A12,1)</f>
+        <v/>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M12">
+        <f>IF(L12="Sí","Cobrado",IF(K12&lt;Resumen!$B$1,"Vencido","Al día"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ferretería El Tornillo</t>
+        </is>
+      </c>
+      <c r="C13">
+        <f>PROPER(TRIM(B13))</f>
+        <v/>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>V02 | Carla Ruiz</t>
+        </is>
+      </c>
+      <c r="E13">
+        <f>_xlfn.TEXTAFTER(D13,"| ")</f>
+        <v/>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>LIM-020</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>50</v>
+      </c>
+      <c r="H13">
+        <f>_xlfn.XLOOKUP(F13,Productos!A:A,Productos!C:C,"Código no existe")</f>
+        <v/>
+      </c>
+      <c r="I13">
+        <f>_xlfn.IFS(G13*H13&gt;=100000,10%,G13*H13&gt;=40000,5%,TRUE,0)</f>
+        <v/>
+      </c>
+      <c r="J13">
+        <f>G13*H13*(1-I13)</f>
+        <v/>
+      </c>
+      <c r="K13" s="3">
+        <f>EOMONTH(A13,1)</f>
+        <v/>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M13">
+        <f>IF(L13="Sí","Cobrado",IF(K13&lt;Resumen!$B$1,"Vencido","Al día"))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38.75" customWidth="1" min="1" max="1"/>
+    <col width="22.5" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="38.75" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Fecha de corte</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="n">
+        <v>46330</v>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Vence</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Neto</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ventas del mes</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="D2" cm="1">
+        <f t="array" ref="D2">IFERROR(_xlfn._xlws.SORT(_xlfn._xlws.FILTER(_xlfn.CHOOSECOLS(Pedidos!A2:M13,3,11,10),Pedidos!M2:M13="Vencido"),3,-1),"Sin vencidos")</f>
+        <v/>
+      </c>
+      <c r="E2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Diego Paz</t>
+        </is>
+      </c>
+      <c r="B3">
+        <f>SUMIFS(Pedidos!J:J,Pedidos!E:E,A3,Pedidos!A:A,"&gt;="&amp;$B$2,Pedidos!A:A,"&lt;="&amp;EOMONTH($B$2,0))</f>
+        <v/>
+      </c>
+      <c r="E3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Carla Ruiz</t>
+        </is>
+      </c>
+      <c r="B4">
+        <f>SUMIFS(Pedidos!J:J,Pedidos!E:E,A4,Pedidos!A:A,"&gt;="&amp;$B$2,Pedidos!A:A,"&lt;="&amp;EOMONTH($B$2,0))</f>
+        <v/>
+      </c>
+      <c r="E4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Tomás Gil</t>
+        </is>
+      </c>
+      <c r="B5">
+        <f>SUMIFS(Pedidos!J:J,Pedidos!E:E,A5,Pedidos!A:A,"&gt;="&amp;$B$2,Pedidos!A:A,"&lt;="&amp;EOMONTH($B$2,0))</f>
+        <v/>
+      </c>
+      <c r="E5" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Vencidas</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" cm="1">
+        <f t="array" ref="A8">_xlfn._xlws.SORT(_xlfn.UNIQUE(Pedidos!C2:C13))</f>
+        <v/>
+      </c>
+      <c r="B8">
+        <f>COUNTIFS(Pedidos!C:C,A8,Pedidos!M:M,"Vencido")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9">
+        <f>COUNTIFS(Pedidos!C:C,A9,Pedidos!M:M,"Vencido")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10">
+        <f>COUNTIFS(Pedidos!C:C,A10,Pedidos!M:M,"Vencido")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11">
+        <f>COUNTIFS(Pedidos!C:C,A11,Pedidos!M:M,"Vencido")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12">
+        <f>COUNTIFS(Pedidos!C:C,A12,Pedidos!M:M,"Vencido")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="23.75" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="21.25" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Código</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Producto</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Precio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>LIM-010</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Cloro 5 L</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="n">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>LIM-020</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Detergente 5 L</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>3100</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>LIM-030</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Desinfectante 1 L</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>LIM-040</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Papel higiénico x48</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>9800</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>PAP-200</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Resma A4</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>PAP-210</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Cuadernos x10</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>6200</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>PAP-220</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Bolígrafos x50</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>3900</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="32.5" customWidth="1" min="2" max="2"/>
+    <col width="112.5" customWidth="1" min="3" max="3"/>
+    <col width="87.5" customWidth="1" min="4" max="4"/>
+    <col width="65" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Fórmula</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Prompt (Mapa · Meta · Prueba)</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Fórmula que dio Claude</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Qué revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>BUSCARX (Mapa + Meta)</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>Excel para la web en español, separador punto y coma. Hoja Pedidos, filas 2 a 13: A Fecha, B Cliente, C Cliente limpio, D Vendedor, E Vendedor limpio, F Código, G Cantidad, H Precio, I Descuento, J Neto, K Vence, L Pagado (Sí/No), M Estado. Catálogo en la hoja Productos: A Código, C Precio. Fecha de corte en Resumen!B1. En H2 quiero el precio de cada código; si no existe, que diga "Código no existe". Una fórmula para copiar hacia abajo.</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>=BUSCARX(F2;Productos!A:A;Productos!C:C;"Código no existe")</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>Que el último argumento cubra los códigos mal escritos; si tu Excel no tiene BUSCARX, pide BUSCARV.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>NOMPROPIO + ESPACIOS (Meta)</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>En C2 quiero el nombre del cliente de B2, prolijo: sin espacios de más y con mayúscula inicial en cada palabra.</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>=NOMPROPIO(ESPACIOS(B2))</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>Siglas (SRL queda Srl) y tildes que faltan: NOMPROPIO no las arregla.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>TEXTODESPUES (Meta)</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>En D2 viene el vendedor así: "V01 | Diego Paz". En E2 quiero solo el nombre.</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>=TEXTODESPUES(D2;"| ")</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Filas sin la barra devuelven #N/A: usa el sexto argumento para dejar el texto original.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>SI.CONJUNTO (Meta)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>En I2 quiero el descuento según el total de la compra (G2*H2): 10 % si llega a 100.000; 5 % si llega a 40.000; si no, 0 %.</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>=SI.CONJUNTO(G2*H2&gt;=100000;10%;G2*H2&gt;=40000;5%;VERDADERO;0)</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>El orden de los tramos (de mayor a menor) y que un precio con error da #¡VALOR!.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>FIN.MES (Meta)</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>En K2 quiero el vencimiento: la condición es pago a fin del mes siguiente a la fecha de A2.</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>=FIN.MES(A2;1)</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>Formato de fecha en la columna (si no, ves 46295); con 0 es fin de este mes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>SUMAR.SI.CONJUNTO (Meta)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>En Resumen tengo los vendedores en A3:A5 y en B2 el primer día del mes que quiero ver. En B3 quiero el neto vendido por ese vendedor en ese mes. Una fórmula para copiar hacia abajo.</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>=SUMAR.SI.CONJUNTO(Pedidos!J:J;Pedidos!E:E;A3;Pedidos!A:A;"&gt;="&amp;$B$2;Pedidos!A:A;"&lt;="&amp;FIN.MES($B$2;0))</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Fechas guardadas como texto no se suman y no avisan: compruébalo con un filtro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>7a</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>SI, estado de cobro, con Mapa + Meta (sin Prueba)</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>En M2 quiero el estado de cada factura: si ya venció a la fecha de corte, que diga "Vencido"; si no, "Al día". Una fórmula para copiar hacia abajo.</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>=SI(K2&lt;Resumen!$B$1;"Vencido";"Al día")</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Es la versión sin Prueba: compárala con la 7b.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>7b</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Prueba sobre la fórmula escrita a mano</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Escribí esta fórmula para M2: =SI(K2&lt;Resumen!$B$1;"Vencido";"Al día"). ¿Qué casos pueden hacer que dé un resultado equivocado sin mostrar error? ¿Qué debería dar la fila 2 (vence 30/09/2026, Pagado: Sí) y la fila 6 (vence 31/10/2026, Pagado: No), con corte 04/11/2026?</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>=SI(L2="Sí";"Cobrado";SI(K2&lt;Resumen!$B$1;"Vencido";"Al día"))</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Que mire la columna Pagado; vencimientos vacíos; vence el mismo día del corte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>FILTRAR + ORDENAR + ELEGIRCOLS (Mapa</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Mapa: el de antes. Meta: en Resumen!D2, una lista que se actualice sola con Cliente (C), Vence (K) y Neto (J) de las facturas "Vencido", de mayor a menor neto. Prueba: antes de darme la fórmula, dime qué casos darían un resultado equivocado sin error y qué debería salir arriba.</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>=SI.ERROR(ORDENAR(FILTRAR(ELEGIRCOLS(Pedidos!A2:M13;3;11;10);Pedidos!M2:M13="Vencido");3;-1);"Sin vencidos")</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Sin vencidas, SI.ERROR; pedidos debajo de la fila 13; deja libres las celdas de abajo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>UNICOS + ORDENAR (Mapa</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Meta: en Resumen!A8, la lista de clientes de Pedidos!C2:C13, sin repetidos y en orden alfabético. Prueba: ¿qué podría salir mal sin error?</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>=ORDENAR(UNICOS(Pedidos!C2:C13))</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Usa la columna limpia: un espacio de más duplica un cliente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>CONTAR.SI.CONJUNTO (Mapa</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Meta: en Resumen!B8, cuántas facturas "Vencido" tiene el cliente de A8 (en Pedidos, el cliente está en C y el estado en M). Para copiar hacia abajo. Prueba: ¿qué podría dar mal sin error?</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>=CONTAR.SI.CONJUNTO(Pedidos!C:C;A8;Pedidos!M:M;"Vencido")</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Un espacio de más en el estado o en el nombre cuenta 0 sin avisar.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -520,1027 +1913,406 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Cliente (sistema)</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Cliente</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Vendedor (sistema)</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Vendedor</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Código</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Cant.</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>Precio</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>Desc.</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>Neto</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>Vence</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>Pagado</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="8" t="n">
         <v>46238</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">  ferretería el TORNILLO </t>
         </is>
       </c>
-      <c r="C2">
-        <f>PROPER(TRIM(B2))</f>
-        <v/>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>V01 | Diego Paz</t>
         </is>
       </c>
-      <c r="E2">
-        <f>_xlfn.TEXTAFTER(D2,"| ")</f>
-        <v/>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>LIM-010</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="H2">
-        <f>_xlfn.XLOOKUP(F2,Productos!A:A,Productos!C:C,"Código no existe")</f>
-        <v/>
-      </c>
-      <c r="I2">
-        <f>_xlfn.IFS(G2*H2&gt;=100000,10%,G2*H2&gt;=40000,5%,TRUE,0)</f>
-        <v/>
-      </c>
-      <c r="J2">
-        <f>G2*H2*(1-I2)</f>
-        <v/>
-      </c>
-      <c r="K2" s="3">
-        <f>EOMONTH(A2,1)</f>
-        <v/>
-      </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" s="6" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="M2">
-        <f>IF(L2="Sí","Cobrado",IF(K2&lt;Resumen!$B$1,"Vencido","Al día"))</f>
-        <v/>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="8" t="n">
         <v>46246</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>LIBRERÍA SAN MARTÍN SRL</t>
         </is>
       </c>
-      <c r="C3">
-        <f>PROPER(TRIM(B3))</f>
-        <v/>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>V02 | Carla Ruiz</t>
         </is>
       </c>
-      <c r="E3">
-        <f>_xlfn.TEXTAFTER(D3,"| ")</f>
-        <v/>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>PAP-200</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" s="6" t="n">
         <v>120</v>
       </c>
-      <c r="H3">
-        <f>_xlfn.XLOOKUP(F3,Productos!A:A,Productos!C:C,"Código no existe")</f>
-        <v/>
-      </c>
-      <c r="I3">
-        <f>_xlfn.IFS(G3*H3&gt;=100000,10%,G3*H3&gt;=40000,5%,TRUE,0)</f>
-        <v/>
-      </c>
-      <c r="J3">
-        <f>G3*H3*(1-I3)</f>
-        <v/>
-      </c>
-      <c r="K3" s="3">
-        <f>EOMONTH(A3,1)</f>
-        <v/>
-      </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="M3">
-        <f>IF(L3="Sí","Cobrado",IF(K3&lt;Resumen!$B$1,"Vencido","Al día"))</f>
-        <v/>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="8" t="n">
         <v>46255</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>kiosco la esquina</t>
         </is>
       </c>
-      <c r="C4">
-        <f>PROPER(TRIM(B4))</f>
-        <v/>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>V03 | Tomás Gil</t>
         </is>
       </c>
-      <c r="E4">
-        <f>_xlfn.TEXTAFTER(D4,"| ")</f>
-        <v/>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>LIM-020</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="H4">
-        <f>_xlfn.XLOOKUP(F4,Productos!A:A,Productos!C:C,"Código no existe")</f>
-        <v/>
-      </c>
-      <c r="I4">
-        <f>_xlfn.IFS(G4*H4&gt;=100000,10%,G4*H4&gt;=40000,5%,TRUE,0)</f>
-        <v/>
-      </c>
-      <c r="J4">
-        <f>G4*H4*(1-I4)</f>
-        <v/>
-      </c>
-      <c r="K4" s="3">
-        <f>EOMONTH(A4,1)</f>
-        <v/>
-      </c>
-      <c r="L4" t="inlineStr">
+      <c r="L4" s="6" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="M4">
-        <f>IF(L4="Sí","Cobrado",IF(K4&lt;Resumen!$B$1,"Vencido","Al día"))</f>
-        <v/>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="8" t="n">
         <v>46267</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">ferretería el tornillo  </t>
         </is>
       </c>
-      <c r="C5">
-        <f>PROPER(TRIM(B5))</f>
-        <v/>
-      </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>V01 | Diego Paz</t>
         </is>
       </c>
-      <c r="E5">
-        <f>_xlfn.TEXTAFTER(D5,"| ")</f>
-        <v/>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>PAP-210</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="H5">
-        <f>_xlfn.XLOOKUP(F5,Productos!A:A,Productos!C:C,"Código no existe")</f>
-        <v/>
-      </c>
-      <c r="I5">
-        <f>_xlfn.IFS(G5*H5&gt;=100000,10%,G5*H5&gt;=40000,5%,TRUE,0)</f>
-        <v/>
-      </c>
-      <c r="J5">
-        <f>G5*H5*(1-I5)</f>
-        <v/>
-      </c>
-      <c r="K5" s="3">
-        <f>EOMONTH(A5,1)</f>
-        <v/>
-      </c>
-      <c r="L5" t="inlineStr">
+      <c r="L5" s="6" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="M5">
-        <f>IF(L5="Sí","Cobrado",IF(K5&lt;Resumen!$B$1,"Vencido","Al día"))</f>
-        <v/>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="8" t="n">
         <v>46274</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">  Colegio Nuevo Horizonte</t>
         </is>
       </c>
-      <c r="C6">
-        <f>PROPER(TRIM(B6))</f>
-        <v/>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>V02 | Carla Ruiz</t>
         </is>
       </c>
-      <c r="E6">
-        <f>_xlfn.TEXTAFTER(D6,"| ")</f>
-        <v/>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>PAP-200</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" s="6" t="n">
         <v>300</v>
       </c>
-      <c r="H6">
-        <f>_xlfn.XLOOKUP(F6,Productos!A:A,Productos!C:C,"Código no existe")</f>
-        <v/>
-      </c>
-      <c r="I6">
-        <f>_xlfn.IFS(G6*H6&gt;=100000,10%,G6*H6&gt;=40000,5%,TRUE,0)</f>
-        <v/>
-      </c>
-      <c r="J6">
-        <f>G6*H6*(1-I6)</f>
-        <v/>
-      </c>
-      <c r="K6" s="3">
-        <f>EOMONTH(A6,1)</f>
-        <v/>
-      </c>
-      <c r="L6" t="inlineStr">
+      <c r="L6" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="M6">
-        <f>IF(L6="Sí","Cobrado",IF(K6&lt;Resumen!$B$1,"Vencido","Al día"))</f>
-        <v/>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="8" t="n">
         <v>46280</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>KIOSCO LA ESQUINA</t>
         </is>
       </c>
-      <c r="C7">
-        <f>PROPER(TRIM(B7))</f>
-        <v/>
-      </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>V03 | Tomás Gil</t>
         </is>
       </c>
-      <c r="E7">
-        <f>_xlfn.TEXTAFTER(D7,"| ")</f>
-        <v/>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>LIM-030</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="H7">
-        <f>_xlfn.XLOOKUP(F7,Productos!A:A,Productos!C:C,"Código no existe")</f>
-        <v/>
-      </c>
-      <c r="I7">
-        <f>_xlfn.IFS(G7*H7&gt;=100000,10%,G7*H7&gt;=40000,5%,TRUE,0)</f>
-        <v/>
-      </c>
-      <c r="J7">
-        <f>G7*H7*(1-I7)</f>
-        <v/>
-      </c>
-      <c r="K7" s="3">
-        <f>EOMONTH(A7,1)</f>
-        <v/>
-      </c>
-      <c r="L7" t="inlineStr">
+      <c r="L7" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="M7">
-        <f>IF(L7="Sí","Cobrado",IF(K7&lt;Resumen!$B$1,"Vencido","Al día"))</f>
-        <v/>
-      </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="8" t="n">
         <v>46288</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">librería san martín srl </t>
         </is>
       </c>
-      <c r="C8">
-        <f>PROPER(TRIM(B8))</f>
-        <v/>
-      </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>V01 | Diego Paz</t>
         </is>
       </c>
-      <c r="E8">
-        <f>_xlfn.TEXTAFTER(D8,"| ")</f>
-        <v/>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>PAP-220</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="H8">
-        <f>_xlfn.XLOOKUP(F8,Productos!A:A,Productos!C:C,"Código no existe")</f>
-        <v/>
-      </c>
-      <c r="I8">
-        <f>_xlfn.IFS(G8*H8&gt;=100000,10%,G8*H8&gt;=40000,5%,TRUE,0)</f>
-        <v/>
-      </c>
-      <c r="J8">
-        <f>G8*H8*(1-I8)</f>
-        <v/>
-      </c>
-      <c r="K8" s="3">
-        <f>EOMONTH(A8,1)</f>
-        <v/>
-      </c>
-      <c r="L8" t="inlineStr">
+      <c r="L8" s="6" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="M8">
-        <f>IF(L8="Sí","Cobrado",IF(K8&lt;Resumen!$B$1,"Vencido","Al día"))</f>
-        <v/>
-      </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="8" t="n">
         <v>46295</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Hotel  Mirador</t>
         </is>
       </c>
-      <c r="C9">
-        <f>PROPER(TRIM(B9))</f>
-        <v/>
-      </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>V01 | Diego Paz</t>
         </is>
       </c>
-      <c r="E9">
-        <f>_xlfn.TEXTAFTER(D9,"| ")</f>
-        <v/>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>LIM-040</t>
         </is>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="H9">
-        <f>_xlfn.XLOOKUP(F9,Productos!A:A,Productos!C:C,"Código no existe")</f>
-        <v/>
-      </c>
-      <c r="I9">
-        <f>_xlfn.IFS(G9*H9&gt;=100000,10%,G9*H9&gt;=40000,5%,TRUE,0)</f>
-        <v/>
-      </c>
-      <c r="J9">
-        <f>G9*H9*(1-I9)</f>
-        <v/>
-      </c>
-      <c r="K9" s="3">
-        <f>EOMONTH(A9,1)</f>
-        <v/>
-      </c>
-      <c r="L9" t="inlineStr">
+      <c r="L9" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="M9">
-        <f>IF(L9="Sí","Cobrado",IF(K9&lt;Resumen!$B$1,"Vencido","Al día"))</f>
-        <v/>
-      </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="8" t="n">
         <v>46301</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>colegio nuevo horizonte</t>
         </is>
       </c>
-      <c r="C10">
-        <f>PROPER(TRIM(B10))</f>
-        <v/>
-      </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>V02 | Carla Ruiz</t>
         </is>
       </c>
-      <c r="E10">
-        <f>_xlfn.TEXTAFTER(D10,"| ")</f>
-        <v/>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>PAP-220</t>
         </is>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" s="6" t="n">
         <v>150</v>
       </c>
-      <c r="H10">
-        <f>_xlfn.XLOOKUP(F10,Productos!A:A,Productos!C:C,"Código no existe")</f>
-        <v/>
-      </c>
-      <c r="I10">
-        <f>_xlfn.IFS(G10*H10&gt;=100000,10%,G10*H10&gt;=40000,5%,TRUE,0)</f>
-        <v/>
-      </c>
-      <c r="J10">
-        <f>G10*H10*(1-I10)</f>
-        <v/>
-      </c>
-      <c r="K10" s="3">
-        <f>EOMONTH(A10,1)</f>
-        <v/>
-      </c>
-      <c r="L10" t="inlineStr">
+      <c r="L10" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="M10">
-        <f>IF(L10="Sí","Cobrado",IF(K10&lt;Resumen!$B$1,"Vencido","Al día"))</f>
-        <v/>
-      </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="8" t="n">
         <v>46309</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">hotel mirador </t>
         </is>
       </c>
-      <c r="C11">
-        <f>PROPER(TRIM(B11))</f>
-        <v/>
-      </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>V03 | Tomás Gil</t>
         </is>
       </c>
-      <c r="E11">
-        <f>_xlfn.TEXTAFTER(D11,"| ")</f>
-        <v/>
-      </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>LIM-040</t>
         </is>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="H11">
-        <f>_xlfn.XLOOKUP(F11,Productos!A:A,Productos!C:C,"Código no existe")</f>
-        <v/>
-      </c>
-      <c r="I11">
-        <f>_xlfn.IFS(G11*H11&gt;=100000,10%,G11*H11&gt;=40000,5%,TRUE,0)</f>
-        <v/>
-      </c>
-      <c r="J11">
-        <f>G11*H11*(1-I11)</f>
-        <v/>
-      </c>
-      <c r="K11" s="3">
-        <f>EOMONTH(A11,1)</f>
-        <v/>
-      </c>
-      <c r="L11" t="inlineStr">
+      <c r="L11" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="M11">
-        <f>IF(L11="Sí","Cobrado",IF(K11&lt;Resumen!$B$1,"Vencido","Al día"))</f>
-        <v/>
-      </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="8" t="n">
         <v>46317</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Kiosco La Esquina</t>
         </is>
       </c>
-      <c r="C12">
-        <f>PROPER(TRIM(B12))</f>
-        <v/>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>V01 | Diego Paz</t>
         </is>
       </c>
-      <c r="E12">
-        <f>_xlfn.TEXTAFTER(D12,"| ")</f>
-        <v/>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>PAP-210</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>PAP-201</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="H12">
-        <f>_xlfn.XLOOKUP(F12,Productos!A:A,Productos!C:C,"Código no existe")</f>
-        <v/>
-      </c>
-      <c r="I12">
-        <f>_xlfn.IFS(G12*H12&gt;=100000,10%,G12*H12&gt;=40000,5%,TRUE,0)</f>
-        <v/>
-      </c>
-      <c r="J12">
-        <f>G12*H12*(1-I12)</f>
-        <v/>
-      </c>
-      <c r="K12" s="3">
-        <f>EOMONTH(A12,1)</f>
-        <v/>
-      </c>
-      <c r="L12" t="inlineStr">
+      <c r="L12" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="M12">
-        <f>IF(L12="Sí","Cobrado",IF(K12&lt;Resumen!$B$1,"Vencido","Al día"))</f>
-        <v/>
-      </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="8" t="n">
         <v>46323</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>Ferretería El Tornillo</t>
         </is>
       </c>
-      <c r="C13">
-        <f>PROPER(TRIM(B13))</f>
-        <v/>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>V02 | Carla Ruiz</t>
         </is>
       </c>
-      <c r="E13">
-        <f>_xlfn.TEXTAFTER(D13,"| ")</f>
-        <v/>
-      </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>LIM-020</t>
         </is>
       </c>
-      <c r="G13" t="n">
+      <c r="G13" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="H13">
-        <f>_xlfn.XLOOKUP(F13,Productos!A:A,Productos!C:C,"Código no existe")</f>
-        <v/>
-      </c>
-      <c r="I13">
-        <f>_xlfn.IFS(G13*H13&gt;=100000,10%,G13*H13&gt;=40000,5%,TRUE,0)</f>
-        <v/>
-      </c>
-      <c r="J13">
-        <f>G13*H13*(1-I13)</f>
-        <v/>
-      </c>
-      <c r="K13" s="3">
-        <f>EOMONTH(A13,1)</f>
-        <v/>
-      </c>
-      <c r="L13" t="inlineStr">
+      <c r="L13" s="6" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
-      </c>
-      <c r="M13">
-        <f>IF(L13="Sí","Cobrado",IF(K13&lt;Resumen!$B$1,"Vencido","Al día"))</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="23.75" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="21.25" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Código</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Producto</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Precio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>LIM-010</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Cloro 5 L</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>2400</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>LIM-020</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Detergente 5 L</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>3100</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>LIM-030</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Desinfectante 1 L</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>1150</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>LIM-040</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Papel higiénico x48</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>9800</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>PAP-200</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Resma A4</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>4500</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>PAP-210</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Cuadernos x10</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>6200</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>PAP-220</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Bolígrafos x50</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>3900</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="38.75" customWidth="1" min="1" max="1"/>
-    <col width="22.5" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="38.75" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Fecha de corte</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="n">
-        <v>46330</v>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>Vence</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>Neto</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Ventas del mes</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>46296</v>
-      </c>
-      <c r="D2" cm="1">
-        <f t="array" ref="D2">IFERROR(_xlfn._xlws.SORT(_xlfn._xlws.FILTER(_xlfn.CHOOSECOLS(Pedidos!A2:M13,3,11,10),Pedidos!M2:M13="Vencido"),3,-1),"Sin vencidos")</f>
-        <v/>
-      </c>
-      <c r="E2" s="3" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Diego Paz</t>
-        </is>
-      </c>
-      <c r="B3">
-        <f>SUMIFS(Pedidos!J:J,Pedidos!E:E,A3,Pedidos!A:A,"&gt;="&amp;$B$2,Pedidos!A:A,"&lt;="&amp;EOMONTH($B$2,0))</f>
-        <v/>
-      </c>
-      <c r="E3" s="3" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Carla Ruiz</t>
-        </is>
-      </c>
-      <c r="B4">
-        <f>SUMIFS(Pedidos!J:J,Pedidos!E:E,A4,Pedidos!A:A,"&gt;="&amp;$B$2,Pedidos!A:A,"&lt;="&amp;EOMONTH($B$2,0))</f>
-        <v/>
-      </c>
-      <c r="E4" s="3" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Tomás Gil</t>
-        </is>
-      </c>
-      <c r="B5">
-        <f>SUMIFS(Pedidos!J:J,Pedidos!E:E,A5,Pedidos!A:A,"&gt;="&amp;$B$2,Pedidos!A:A,"&lt;="&amp;EOMONTH($B$2,0))</f>
-        <v/>
-      </c>
-      <c r="E5" s="3" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Vencidas</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" cm="1">
-        <f t="array" ref="A8">_xlfn._xlws.SORT(_xlfn.UNIQUE(Pedidos!C2:C13))</f>
-        <v/>
-      </c>
-      <c r="B8">
-        <f>COUNTIFS(Pedidos!C:C,A8,Pedidos!M:M,"Vencido")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9">
-        <f>COUNTIFS(Pedidos!C:C,A9,Pedidos!M:M,"Vencido")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10">
-        <f>COUNTIFS(Pedidos!C:C,A10,Pedidos!M:M,"Vencido")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11">
-        <f>COUNTIFS(Pedidos!C:C,A11,Pedidos!M:M,"Vencido")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12">
-        <f>COUNTIFS(Pedidos!C:C,A12,Pedidos!M:M,"Vencido")</f>
-        <v/>
       </c>
     </row>
   </sheetData>
